--- a/lookups/list_of_occupation_expected_monthly_income.xlsx
+++ b/lookups/list_of_occupation_expected_monthly_income.xlsx
@@ -1,43 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\bot-report-2026\mapper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\western-union-bot-report-2026\lookups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A2197D-33B6-4661-B3F3-F9F35CE499B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E8AC2F-5A36-4406-B558-7DEEE9AF0C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="2475" windowWidth="17415" windowHeight="11265" xr2:uid="{589DB96B-7233-49CE-B0E4-9A63ED72E852}"/>
+    <workbookView xWindow="5130" yWindow="3495" windowWidth="16185" windowHeight="11295" xr2:uid="{589DB96B-7233-49CE-B0E4-9A63ED72E852}"/>
   </bookViews>
   <sheets>
     <sheet name="Occupation" sheetId="1" r:id="rId1"/>
     <sheet name="Transaction purpose" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="168">
   <si>
     <t>Value Displayed on UI (in English)</t>
   </si>
@@ -417,10 +406,130 @@
     <t>5,000 – 9,000</t>
   </si>
   <si>
-    <t>0 – 5,000</t>
-  </si>
-  <si>
     <t>Expected Monthly Income</t>
+  </si>
+  <si>
+    <t>BoT code</t>
+  </si>
+  <si>
+    <t>Airline</t>
+  </si>
+  <si>
+    <t>Maritime Employee</t>
+  </si>
+  <si>
+    <t>Art</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Sports Professional</t>
+  </si>
+  <si>
+    <t>Civil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Government Employee </t>
+  </si>
+  <si>
+    <t>Teacher</t>
+  </si>
+  <si>
+    <t>Educator</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>Restaurant</t>
+  </si>
+  <si>
+    <t>Leisure Services Employee</t>
+  </si>
+  <si>
+    <t>Housewife</t>
+  </si>
+  <si>
+    <t>Child Care</t>
+  </si>
+  <si>
+    <t>Laborer-Oil</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Mining</t>
+  </si>
+  <si>
+    <t>Forestry</t>
+  </si>
+  <si>
+    <t>Cosmetic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal Care Services </t>
+  </si>
+  <si>
+    <t>Law Enforcement</t>
+  </si>
+  <si>
+    <t>Military Professional</t>
+  </si>
+  <si>
+    <t>Religious</t>
+  </si>
+  <si>
+    <t>Church Servant</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Real Estate Professional</t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
+    <t>Research Professional</t>
+  </si>
+  <si>
+    <t>Skilled Trade</t>
+  </si>
+  <si>
+    <t>Specialist</t>
+  </si>
+  <si>
+    <t>BUSINESS OWNER</t>
+  </si>
+  <si>
+    <t>CIVIL SERVANT</t>
+  </si>
+  <si>
+    <t>COMPANY EMPLOYEE</t>
+  </si>
+  <si>
+    <t>FREELANCE</t>
+  </si>
+  <si>
+    <t>NON-OFFICE EMPLOYEE</t>
+  </si>
+  <si>
+    <t>STATE ENTERPRISE EMPLOYEE</t>
+  </si>
+  <si>
+    <t>STUDENT</t>
+  </si>
+  <si>
+    <t>OTHERS</t>
   </si>
 </sst>
 </file>
@@ -838,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC73E40F-ACAB-46AF-974A-476CBD7E7543}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultColWidth="42.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.140625" style="4" customWidth="1"/>
@@ -848,7 +957,7 @@
     <col min="7" max="16384" width="42.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
+    <row r="1" spans="1:7" ht="15.75">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -865,10 +974,13 @@
         <v>88</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -887,353 +999,407 @@
       <c r="F2" s="6">
         <v>35000</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="4">
+        <v>2003500008</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2">
+        <v>25000</v>
+      </c>
+      <c r="D3" s="2">
+        <v>25000</v>
+      </c>
+      <c r="E3" s="2">
+        <v>25000</v>
+      </c>
+      <c r="F3" s="6">
+        <v>35000</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2003500008</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>25000</v>
+      </c>
+      <c r="D4" s="2">
+        <v>25000</v>
+      </c>
+      <c r="E4" s="2">
+        <v>25000</v>
+      </c>
+      <c r="F4" s="6">
+        <v>35000</v>
+      </c>
+      <c r="G4" s="4">
+        <v>2003500008</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2">
-        <v>25000</v>
-      </c>
-      <c r="D3" s="2">
-        <v>25000</v>
-      </c>
-      <c r="E3" s="2">
-        <v>25000</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="C5" s="3">
+        <v>25000</v>
+      </c>
+      <c r="D5" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E5" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F5" s="6">
         <v>30000</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="G5" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>25000</v>
+      </c>
+      <c r="D6" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E6" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F6" s="6">
+        <v>30000</v>
+      </c>
+      <c r="G6" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3">
+        <v>25000</v>
+      </c>
+      <c r="D7" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E7" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F7" s="6">
+        <v>30000</v>
+      </c>
+      <c r="G7" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>25000</v>
+      </c>
+      <c r="D8" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F8" s="6">
+        <v>30000</v>
+      </c>
+      <c r="G8" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3">
+        <v>25000</v>
+      </c>
+      <c r="D9" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F9" s="6">
+        <v>30000</v>
+      </c>
+      <c r="G9" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2">
-        <v>25000</v>
-      </c>
-      <c r="D4" s="2">
-        <v>25000</v>
-      </c>
-      <c r="E4" s="2">
-        <v>25000</v>
-      </c>
-      <c r="F4" s="6">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
+      <c r="C10" s="3">
+        <v>25000</v>
+      </c>
+      <c r="D10" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F10" s="6">
+        <v>25000</v>
+      </c>
+      <c r="G10" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3">
+        <v>25000</v>
+      </c>
+      <c r="D11" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E11" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F11" s="6">
+        <v>25000</v>
+      </c>
+      <c r="G11" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="D12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F12" s="6">
+        <v>25000</v>
+      </c>
+      <c r="G12" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F13" s="6">
         <v>12000</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="G13" s="4">
+        <v>2003500012</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F14" s="6">
         <v>18000</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
+      <c r="G14" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F15" s="6">
         <v>28000</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
+      <c r="G15" s="4">
+        <v>2003500005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="6">
+        <v>28000</v>
+      </c>
+      <c r="G16" s="4">
+        <v>2003500005</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" s="6">
+        <v>28000</v>
+      </c>
+      <c r="G17" s="4">
+        <v>2003500005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F18" s="6">
         <v>18000</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="G18" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F9" s="6">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F10" s="6">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F11" s="6">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="F19" s="6">
         <v>18000</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="6">
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F14" s="6">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F15" s="6">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F16" s="6">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" s="6">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="6">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F19" s="6">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>89</v>
@@ -1245,35 +1411,41 @@
         <v>91</v>
       </c>
       <c r="F20" s="6">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>18000</v>
+      </c>
+      <c r="G20" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="4" t="s">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="F21" s="6">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>18000</v>
+      </c>
+      <c r="G21" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>89</v>
@@ -1285,55 +1457,64 @@
         <v>91</v>
       </c>
       <c r="F22" s="6">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>12000</v>
+      </c>
+      <c r="G22" s="4">
+        <v>2003500012</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="4" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="F23" s="6">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>12000</v>
+      </c>
+      <c r="G23" s="4">
+        <v>2003500012</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>89</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="F24" s="6">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>12000</v>
+      </c>
+      <c r="G24" s="4">
+        <v>2003500012</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="4" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>98</v>
@@ -1345,107 +1526,946 @@
         <v>100</v>
       </c>
       <c r="F25" s="6">
+        <v>45000</v>
+      </c>
+      <c r="G25" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="6">
+        <v>12000</v>
+      </c>
+      <c r="G26" s="4">
+        <v>2003500009</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="6">
+        <v>18000</v>
+      </c>
+      <c r="G27" s="4">
+        <v>2003500011</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="6">
+        <v>16000</v>
+      </c>
+      <c r="G28" s="4">
+        <v>2003500011</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="6">
+        <v>45000</v>
+      </c>
+      <c r="G29" s="4">
+        <v>2003500011</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" s="7">
+        <v>45000</v>
+      </c>
+      <c r="G30" s="4">
+        <v>2003500011</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" s="4">
+        <v>45000</v>
+      </c>
+      <c r="G31" s="4">
+        <v>2003500011</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" s="4">
+        <v>45000</v>
+      </c>
+      <c r="G32" s="4">
+        <v>2003500011</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F33" s="4">
+        <v>45000</v>
+      </c>
+      <c r="G33" s="4">
+        <v>2003500011</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" s="4">
+        <v>40000</v>
+      </c>
+      <c r="G34" s="4">
+        <v>2003500007</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F35" s="4">
+        <v>22000</v>
+      </c>
+      <c r="G35" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F36" s="4">
+        <v>22000</v>
+      </c>
+      <c r="G36" s="4">
+        <v>2003500010</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F37" s="4">
+        <v>22000</v>
+      </c>
+      <c r="G37" s="4">
+        <v>2003500010</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F38" s="4">
+        <v>22000</v>
+      </c>
+      <c r="G38" s="4">
+        <v>2003500010</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F39" s="4">
+        <v>28000</v>
+      </c>
+      <c r="G39" s="4">
+        <v>2003500003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" s="4">
+        <v>28000</v>
+      </c>
+      <c r="G40" s="4">
+        <v>2003500003</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F41" s="4">
+        <v>28000</v>
+      </c>
+      <c r="G41" s="4">
+        <v>2003500003</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F42" s="4">
+        <v>30000</v>
+      </c>
+      <c r="G42" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F43" s="4">
+        <v>25000</v>
+      </c>
+      <c r="G43" s="4">
+        <v>2003500010</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F44" s="4">
+        <v>15000</v>
+      </c>
+      <c r="G44" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F45" s="4">
+        <v>15000</v>
+      </c>
+      <c r="G45" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F46" s="4">
+        <v>15000</v>
+      </c>
+      <c r="G46" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" s="4">
+        <v>18000</v>
+      </c>
+      <c r="G47" s="4">
+        <v>2003500010</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F48" s="4">
+        <v>20000</v>
+      </c>
+      <c r="G48" s="4">
+        <v>2003500014</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F49" s="4">
         <v>35000</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="4" t="s">
+      <c r="G49" s="4">
+        <v>2003500010</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F50" s="4">
+        <v>35000</v>
+      </c>
+      <c r="G50" s="4">
+        <v>2003500010</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F51" s="4">
+        <v>35000</v>
+      </c>
+      <c r="G51" s="4">
+        <v>2003500010</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F52" s="4">
+        <v>35000</v>
+      </c>
+      <c r="G52" s="4">
+        <v>2003500010</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F53" s="4">
+        <v>35000</v>
+      </c>
+      <c r="G53" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F54" s="4">
+        <v>35000</v>
+      </c>
+      <c r="G54" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F55" s="4">
+        <v>35000</v>
+      </c>
+      <c r="G55" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B56" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C56" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D56" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E56" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F56" s="4">
         <v>15000</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="4" t="s">
+      <c r="G56" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B57" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C57" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D57" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E57" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F57" s="4">
         <v>30000</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="4" t="s">
+      <c r="G57" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B58" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C58" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D58" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E58" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F28" s="6">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="4" t="s">
+      <c r="F58" s="4">
+        <v>25000</v>
+      </c>
+      <c r="G58" s="4">
+        <v>2003500011</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F59" s="4">
+        <v>25000</v>
+      </c>
+      <c r="G59" s="4">
+        <v>2003500011</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F60" s="4">
+        <v>25000</v>
+      </c>
+      <c r="G60" s="4">
+        <v>2003500011</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B61" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C61" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D61" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E61" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F61" s="4">
         <v>8000</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="4" t="s">
+      <c r="G61" s="4">
+        <v>2003500013</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B62" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C62" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D62" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E62" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>126</v>
+      <c r="F62" s="4">
+        <v>5000</v>
+      </c>
+      <c r="G62" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F63" s="4">
+        <v>45000</v>
+      </c>
+      <c r="G63" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F64" s="4">
+        <v>25000</v>
+      </c>
+      <c r="G64" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F65" s="4">
+        <v>45000</v>
+      </c>
+      <c r="G65" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F66" s="4">
+        <v>45000</v>
+      </c>
+      <c r="G66" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F67" s="4">
+        <v>45000</v>
+      </c>
+      <c r="G67" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F68" s="4">
+        <v>25000</v>
+      </c>
+      <c r="G68" s="4">
+        <v>2003500015</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F69" s="4">
+        <v>8000</v>
+      </c>
+      <c r="G69" s="4">
+        <v>2003500013</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G70" s="4">
+        <v>2003500015</v>
       </c>
     </row>
   </sheetData>
